--- a/Data/TemplateFile.xlsx
+++ b/Data/TemplateFile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenna\Downloads\SpareParts and Salesprice calculationV2 27112023\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenna\Desktop\MS\Marvu\Automations\SpareParts and Salesprice calculation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708D1F17-B1B3-4265-9A96-CF21AF87CE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AA2F48-76C0-4369-84FD-22A7FA34BF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2240" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spareparts incl price" sheetId="8" r:id="rId1"/>
@@ -86,7 +86,7 @@
     <t>Cost price a piece</t>
   </si>
   <si>
-    <t>Validity: 90 days</t>
+    <t>Validity: 30 days</t>
   </si>
 </sst>
 </file>
@@ -743,45 +743,45 @@
     <tabColor rgb="FF97C222"/>
   </sheetPr>
   <dimension ref="A1:L95"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="14" customWidth="1"/>
-    <col min="4" max="5" width="30.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.77734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="38.77734375" style="2" customWidth="1"/>
-    <col min="9" max="10" width="20.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="14" customWidth="1"/>
+    <col min="4" max="5" width="30.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="38.7109375" style="2" customWidth="1"/>
+    <col min="9" max="10" width="20.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C1" s="13"/>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="4"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E3" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E4" s="11" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E5" s="11" t="s">
         <v>5</v>
       </c>
@@ -792,7 +792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
@@ -827,7 +827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="15"/>
@@ -840,7 +840,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="15"/>
@@ -853,7 +853,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="15"/>
@@ -867,7 +867,7 @@
       <c r="K10" s="7"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="15"/>
@@ -880,7 +880,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="15"/>
@@ -893,7 +893,7 @@
       <c r="J12" s="6"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="15"/>
@@ -906,7 +906,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="15"/>
@@ -919,7 +919,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="15"/>
@@ -932,7 +932,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="15"/>
@@ -945,7 +945,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="15"/>
@@ -958,7 +958,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="15"/>
@@ -971,7 +971,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="15"/>
@@ -984,7 +984,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="15"/>
@@ -997,7 +997,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="15"/>
@@ -1010,7 +1010,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="15"/>
@@ -1023,7 +1023,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="15"/>
@@ -1036,7 +1036,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="15"/>
@@ -1049,7 +1049,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="15"/>
@@ -1062,7 +1062,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="15"/>
@@ -1075,7 +1075,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="15"/>
@@ -1088,7 +1088,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="15"/>
@@ -1101,7 +1101,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="15"/>
@@ -1114,7 +1114,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="15"/>
@@ -1127,7 +1127,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="7"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="15"/>
@@ -1140,7 +1140,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="15"/>
@@ -1153,7 +1153,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="15"/>
@@ -1166,7 +1166,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="15"/>
@@ -1179,7 +1179,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="7"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="15"/>
@@ -1192,7 +1192,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="15"/>
@@ -1205,7 +1205,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="7"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="15"/>
@@ -1218,7 +1218,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="15"/>
@@ -1231,7 +1231,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="7"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="15"/>
@@ -1244,7 +1244,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="15"/>
@@ -1257,7 +1257,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="7"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="15"/>
@@ -1270,7 +1270,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="15"/>
@@ -1283,7 +1283,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="7"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="15"/>
@@ -1296,7 +1296,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="15"/>
@@ -1309,7 +1309,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="7"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="15"/>
@@ -1322,7 +1322,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="7"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="15"/>
@@ -1335,7 +1335,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="7"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="15"/>
@@ -1348,7 +1348,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="7"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="15"/>
@@ -1361,7 +1361,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="7"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="15"/>
@@ -1374,7 +1374,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="7"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="15"/>
@@ -1387,7 +1387,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="7"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="15"/>
@@ -1400,7 +1400,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="7"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="15"/>
@@ -1413,7 +1413,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="7"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="15"/>
@@ -1426,7 +1426,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="7"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="15"/>
@@ -1439,7 +1439,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="7"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="15"/>
@@ -1452,7 +1452,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="7"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="15"/>
@@ -1465,7 +1465,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="7"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="15"/>
@@ -1478,7 +1478,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="15"/>
@@ -1491,7 +1491,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="7"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="15"/>
@@ -1504,7 +1504,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="7"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="15"/>
@@ -1517,7 +1517,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="7"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="15"/>
@@ -1530,7 +1530,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="7"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="15"/>
@@ -1543,7 +1543,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="15"/>
@@ -1556,7 +1556,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="7"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="15"/>
@@ -1569,7 +1569,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="15"/>
@@ -1582,7 +1582,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="15"/>
@@ -1595,7 +1595,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="7"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="15"/>
@@ -1608,7 +1608,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="15"/>
@@ -1621,7 +1621,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="7"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="15"/>
@@ -1634,7 +1634,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="15"/>
@@ -1647,7 +1647,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="7"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="15"/>
@@ -1660,7 +1660,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="15"/>
@@ -1673,7 +1673,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="7"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="15"/>
@@ -1686,7 +1686,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="7"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="15"/>
@@ -1699,7 +1699,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="7"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="15"/>
@@ -1712,7 +1712,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="7"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="15"/>
@@ -1725,7 +1725,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="7"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="15"/>
@@ -1738,7 +1738,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="15"/>
@@ -1751,7 +1751,7 @@
       <c r="J78" s="6"/>
       <c r="K78" s="7"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="15"/>
@@ -1764,7 +1764,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="7"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="15"/>
@@ -1777,7 +1777,7 @@
       <c r="J80" s="6"/>
       <c r="K80" s="7"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="15"/>
@@ -1790,7 +1790,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="7"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="15"/>
@@ -1803,7 +1803,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="7"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="15"/>
@@ -1816,7 +1816,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="7"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="15"/>
@@ -1829,7 +1829,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="7"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="15"/>
@@ -1842,7 +1842,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="7"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="15"/>
@@ -1855,7 +1855,7 @@
       <c r="J86" s="6"/>
       <c r="K86" s="7"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="15"/>
@@ -1868,7 +1868,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="7"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="15"/>
@@ -1881,7 +1881,7 @@
       <c r="J88" s="6"/>
       <c r="K88" s="7"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="15"/>
@@ -1894,7 +1894,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="7"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="15"/>
@@ -1907,7 +1907,7 @@
       <c r="J90" s="6"/>
       <c r="K90" s="7"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="15"/>
@@ -1920,7 +1920,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="7"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="15"/>
@@ -1933,7 +1933,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="7"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="15"/>
@@ -1946,7 +1946,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="7"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="15"/>
@@ -1959,7 +1959,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="7"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="15"/>
